--- a/src/aw-daniel/01_analiza_wstepna/dualizm_polski.xlsx
+++ b/src/aw-daniel/01_analiza_wstepna/dualizm_polski.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-daniel\01_analiza wstepna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dapha\Desktop\Repositories\poland-ab-mda\src\aw-daniel\01_analiza_wstepna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A02F90-9182-4B29-B5C2-D86A9E8C676D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8533B69-23C5-4531-AA59-D06AFC3F9B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9216B270-1592-44E7-A247-948A20CDD3EC}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{9216B270-1592-44E7-A247-948A20CDD3EC}"/>
   </bookViews>
   <sheets>
     <sheet name="OPIS" sheetId="1" r:id="rId1"/>
